--- a/artfynd/A 1760-2023 artfynd.xlsx
+++ b/artfynd/A 1760-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1760-2023 artfynd.xlsx
+++ b/artfynd/A 1760-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1154,6 +1154,1026 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>118069342</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100984</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221223</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vippärt</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lathyrus niger</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Marma-Visteby, Länna, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>664560</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6641091</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-06-03</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-06-03</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>118069414</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101000</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Marma-Visteby, Länna, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>664627</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6641154</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>118069411</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101000</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Marma-Visteby, Länna, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>664625</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6641137</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>118069341</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100984</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221223</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vippärt</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lathyrus niger</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Marma-Visteby, Länna, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>664550</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6641085</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-06-03</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-06-03</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>118069412</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100007</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Marma-Visteby, Länna, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>664623</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6641144</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>118069416</v>
+      </c>
+      <c r="B11" t="n">
+        <v>104842</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Marma-Visteby, Länna, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>664642</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6641174</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>118069415</v>
+      </c>
+      <c r="B12" t="n">
+        <v>101000</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Marma-Visteby, Länna, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>664639</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6641170</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>118069421</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79561</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Marma-Visteby, Länna, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>664639</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6641212</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>118069614</v>
+      </c>
+      <c r="B14" t="n">
+        <v>56249</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>208255</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Skogsödla</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Zootoca vivipara</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Marma-Visteby, Länna, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>664643</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6641176</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>118069343</v>
+      </c>
+      <c r="B15" t="n">
+        <v>100984</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221223</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vippärt</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lathyrus niger</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Marma-Visteby, Länna, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>664589</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6641101</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-06-03</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-06-03</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 1760-2023 artfynd.xlsx
+++ b/artfynd/A 1760-2023 artfynd.xlsx
@@ -1156,10 +1156,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118069342</v>
+        <v>118069421</v>
       </c>
       <c r="B6" t="n">
-        <v>100984</v>
+        <v>79561</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1172,21 +1172,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221223</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>664560</v>
+        <v>664639</v>
       </c>
       <c r="R6" t="n">
-        <v>6641091</v>
+        <v>6641212</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1360,7 +1360,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118069411</v>
+        <v>118069415</v>
       </c>
       <c r="B8" t="n">
         <v>101000</v>
@@ -1400,10 +1400,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>664625</v>
+        <v>664639</v>
       </c>
       <c r="R8" t="n">
-        <v>6641137</v>
+        <v>6641170</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1462,7 +1462,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118069341</v>
+        <v>118069343</v>
       </c>
       <c r="B9" t="n">
         <v>100984</v>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>664550</v>
+        <v>664589</v>
       </c>
       <c r="R9" t="n">
-        <v>6641085</v>
+        <v>6641101</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1564,10 +1564,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118069412</v>
+        <v>118069411</v>
       </c>
       <c r="B10" t="n">
-        <v>100007</v>
+        <v>101000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1580,21 +1580,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>664623</v>
+        <v>664625</v>
       </c>
       <c r="R10" t="n">
-        <v>6641144</v>
+        <v>6641137</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1666,10 +1666,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118069416</v>
+        <v>118069341</v>
       </c>
       <c r="B11" t="n">
-        <v>104842</v>
+        <v>100984</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1678,25 +1678,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221141</v>
+        <v>221223</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Vippärt</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Lathyrus niger</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1706,10 +1706,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>664642</v>
+        <v>664550</v>
       </c>
       <c r="R11" t="n">
-        <v>6641174</v>
+        <v>6641085</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1736,12 +1736,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1768,10 +1768,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118069415</v>
+        <v>118069416</v>
       </c>
       <c r="B12" t="n">
-        <v>101000</v>
+        <v>104842</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1784,21 +1784,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221235</v>
+        <v>221141</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1808,10 +1808,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>664639</v>
+        <v>664642</v>
       </c>
       <c r="R12" t="n">
-        <v>6641170</v>
+        <v>6641174</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1870,10 +1870,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118069421</v>
+        <v>118069412</v>
       </c>
       <c r="B13" t="n">
-        <v>79561</v>
+        <v>100007</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1882,25 +1882,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>222771</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1910,10 +1910,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>664639</v>
+        <v>664623</v>
       </c>
       <c r="R13" t="n">
-        <v>6641212</v>
+        <v>6641144</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1972,10 +1972,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118069614</v>
+        <v>118069342</v>
       </c>
       <c r="B14" t="n">
-        <v>56249</v>
+        <v>100984</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1984,25 +1984,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>208255</v>
+        <v>221223</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Vippärt</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Lathyrus niger</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2012,10 +2012,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>664643</v>
+        <v>664560</v>
       </c>
       <c r="R14" t="n">
-        <v>6641176</v>
+        <v>6641091</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2042,12 +2042,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2074,10 +2074,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118069343</v>
+        <v>118069614</v>
       </c>
       <c r="B15" t="n">
-        <v>100984</v>
+        <v>56249</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2086,25 +2086,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221223</v>
+        <v>208255</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>664589</v>
+        <v>664643</v>
       </c>
       <c r="R15" t="n">
-        <v>6641101</v>
+        <v>6641176</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2144,12 +2144,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 1760-2023 artfynd.xlsx
+++ b/artfynd/A 1760-2023 artfynd.xlsx
@@ -1057,7 +1057,7 @@
         <v>117555477</v>
       </c>
       <c r="B5" t="n">
-        <v>100984</v>
+        <v>100986</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1156,10 +1156,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118069421</v>
+        <v>118069614</v>
       </c>
       <c r="B6" t="n">
-        <v>79561</v>
+        <v>56249</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1168,25 +1168,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>208255</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>664639</v>
+        <v>664643</v>
       </c>
       <c r="R6" t="n">
-        <v>6641212</v>
+        <v>6641176</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118069414</v>
+        <v>118069341</v>
       </c>
       <c r="B7" t="n">
-        <v>101000</v>
+        <v>100986</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,20 +1270,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221235</v>
+        <v>221223</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vippärt</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lathyrus niger</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>664627</v>
+        <v>664550</v>
       </c>
       <c r="R7" t="n">
-        <v>6641154</v>
+        <v>6641085</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1328,12 +1328,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118069415</v>
+        <v>118069416</v>
       </c>
       <c r="B8" t="n">
-        <v>101000</v>
+        <v>104844</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1376,21 +1376,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221235</v>
+        <v>221141</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1400,10 +1400,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>664639</v>
+        <v>664642</v>
       </c>
       <c r="R8" t="n">
-        <v>6641170</v>
+        <v>6641174</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1462,10 +1462,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118069343</v>
+        <v>118069412</v>
       </c>
       <c r="B9" t="n">
-        <v>100984</v>
+        <v>100009</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1474,25 +1474,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221223</v>
+        <v>222771</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>664589</v>
+        <v>664623</v>
       </c>
       <c r="R9" t="n">
-        <v>6641101</v>
+        <v>6641144</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1564,10 +1564,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118069411</v>
+        <v>118069421</v>
       </c>
       <c r="B10" t="n">
-        <v>101000</v>
+        <v>79563</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1576,25 +1576,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221235</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>664625</v>
+        <v>664639</v>
       </c>
       <c r="R10" t="n">
-        <v>6641137</v>
+        <v>6641212</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1666,10 +1666,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118069341</v>
+        <v>118069411</v>
       </c>
       <c r="B11" t="n">
-        <v>100984</v>
+        <v>101002</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1678,20 +1678,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221223</v>
+        <v>221235</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1706,10 +1706,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>664550</v>
+        <v>664625</v>
       </c>
       <c r="R11" t="n">
-        <v>6641085</v>
+        <v>6641137</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1736,12 +1736,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1768,10 +1768,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118069416</v>
+        <v>118069342</v>
       </c>
       <c r="B12" t="n">
-        <v>104842</v>
+        <v>100986</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1780,25 +1780,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221141</v>
+        <v>221223</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Vippärt</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Lathyrus niger</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1808,10 +1808,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>664642</v>
+        <v>664560</v>
       </c>
       <c r="R12" t="n">
-        <v>6641174</v>
+        <v>6641091</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1838,12 +1838,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1870,10 +1870,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118069412</v>
+        <v>118069415</v>
       </c>
       <c r="B13" t="n">
-        <v>100007</v>
+        <v>101002</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1886,21 +1886,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1910,10 +1910,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>664623</v>
+        <v>664639</v>
       </c>
       <c r="R13" t="n">
-        <v>6641144</v>
+        <v>6641170</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1972,10 +1972,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118069342</v>
+        <v>118069343</v>
       </c>
       <c r="B14" t="n">
-        <v>100984</v>
+        <v>100986</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2012,10 +2012,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>664560</v>
+        <v>664589</v>
       </c>
       <c r="R14" t="n">
-        <v>6641091</v>
+        <v>6641101</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2074,10 +2074,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118069614</v>
+        <v>118069414</v>
       </c>
       <c r="B15" t="n">
-        <v>56249</v>
+        <v>101002</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2090,21 +2090,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>208255</v>
+        <v>221235</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>664643</v>
+        <v>664627</v>
       </c>
       <c r="R15" t="n">
-        <v>6641176</v>
+        <v>6641154</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2144,12 +2144,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 1760-2023 artfynd.xlsx
+++ b/artfynd/A 1760-2023 artfynd.xlsx
@@ -1156,10 +1156,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118069614</v>
+        <v>118069341</v>
       </c>
       <c r="B6" t="n">
-        <v>56249</v>
+        <v>100986</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1168,25 +1168,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>208255</v>
+        <v>221223</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Vippärt</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Lathyrus niger</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>664643</v>
+        <v>664550</v>
       </c>
       <c r="R6" t="n">
-        <v>6641176</v>
+        <v>6641085</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118069341</v>
+        <v>118069614</v>
       </c>
       <c r="B7" t="n">
-        <v>100986</v>
+        <v>56249</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,25 +1270,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221223</v>
+        <v>208255</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>664550</v>
+        <v>664643</v>
       </c>
       <c r="R7" t="n">
-        <v>6641085</v>
+        <v>6641176</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1328,12 +1328,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 1760-2023 artfynd.xlsx
+++ b/artfynd/A 1760-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2174,6 +2174,113 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>124825180</v>
+      </c>
+      <c r="B16" t="n">
+        <v>101167</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221223</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vippärt</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lathyrus niger</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ältsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>664553</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6641084</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Känd förekomst.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 1760-2023 artfynd.xlsx
+++ b/artfynd/A 1760-2023 artfynd.xlsx
@@ -2179,7 +2179,7 @@
         <v>124825180</v>
       </c>
       <c r="B16" t="n">
-        <v>101167</v>
+        <v>101339</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 1760-2023 artfynd.xlsx
+++ b/artfynd/A 1760-2023 artfynd.xlsx
@@ -2181,11 +2181,6 @@
       <c r="B16" t="n">
         <v>101339</v>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>NT</t>
